--- a/config.xlsx
+++ b/config.xlsx
@@ -1493,7 +1493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1505,16 +1505,17 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1565,50 +1566,55 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>storm_frac</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>standoff_nm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>idle_h</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>optimize_param</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>optimize_lo</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>optimize_hi</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>optimize_n</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>sweep_param</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>sweep_lo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>sweep_hi</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>sweep_n</t>
         </is>
@@ -1649,32 +1655,32 @@
       <c r="H2" t="n">
         <v>18</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>22</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>18</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>500</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>18000</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1713,32 +1719,32 @@
       <c r="H3" t="n">
         <v>18</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>22</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>18</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>500</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>18000</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1777,35 +1783,32 @@
       <c r="H4" t="n">
         <v>18</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>5</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>22</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>18</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>500</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>18000</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1844,35 +1847,32 @@
       <c r="H5" t="n">
         <v>18</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>22</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>18</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>500</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>18000</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1908,32 +1908,32 @@
       <c r="G6" t="n">
         <v>0.2</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>5</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>22</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>18</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>500</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>18000</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1969,32 +1969,32 @@
       <c r="G7" t="n">
         <v>0.2</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>22</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>18</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>500</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>18000</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2033,32 +2033,32 @@
       <c r="H8" t="n">
         <v>18</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>5</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>22</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>18</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>500</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>18000</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2101,37 +2101,40 @@
         <v>12</v>
       </c>
       <c r="J9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K9" t="n">
         <v>200</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>12</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>op_v_kn</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>5</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>22</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>18</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>d_km</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>500</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>18000</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>36</v>
       </c>
     </row>
@@ -2174,9 +2177,12 @@
         <v>12</v>
       </c>
       <c r="J10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K10" t="n">
         <v>200</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>12</v>
       </c>
     </row>

--- a/config.xlsx
+++ b/config.xlsx
@@ -1504,8 +1504,8 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>storm_duration_h</t>
+          <t>detach_duration_h</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>storm_frac</t>
+          <t>detach_frac</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
